--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,9 +790,126 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136867616</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93423</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sunnorpegölen, Sunnorpegölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>536432</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6493245</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stjärnorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136867616</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136863103</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867616</v>
       </c>
       <c r="B3" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136863103</v>
       </c>
       <c r="B2" t="n">
-        <v>97632</v>
+        <v>97634</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867616</v>
       </c>
       <c r="B3" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136863103</v>
       </c>
       <c r="B2" t="n">
-        <v>97634</v>
+        <v>97635</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867616</v>
       </c>
       <c r="B3" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136863103</v>
       </c>
       <c r="B2" t="n">
-        <v>97635</v>
+        <v>97641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867616</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136863103</v>
       </c>
       <c r="B2" t="n">
-        <v>97641</v>
+        <v>97645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867616</v>
       </c>
       <c r="B3" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136863103</v>
       </c>
       <c r="B2" t="n">
-        <v>97645</v>
+        <v>97647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136863103</v>
       </c>
       <c r="B2" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867616</v>
       </c>
       <c r="B3" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136863103</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867616</v>
       </c>
       <c r="B3" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136863103</v>
       </c>
       <c r="B2" t="n">
-        <v>97662</v>
+        <v>97664</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867616</v>
       </c>
       <c r="B3" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -830,11 +830,7 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sunnorpegölen, Sunnorpegölen, Ög</t>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136863103</v>
       </c>
       <c r="B2" t="n">
-        <v>97664</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867616</v>
       </c>
       <c r="B3" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136863103</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867616</v>
       </c>
       <c r="B3" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136863103</v>
       </c>
       <c r="B2" t="n">
-        <v>97677</v>
+        <v>97678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867616</v>
       </c>
       <c r="B3" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136863103</v>
       </c>
       <c r="B2" t="n">
-        <v>97678</v>
+        <v>97683</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867616</v>
       </c>
       <c r="B3" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136863103</v>
       </c>
       <c r="B2" t="n">
-        <v>97683</v>
+        <v>97685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867616</v>
       </c>
       <c r="B3" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136863103</v>
       </c>
       <c r="B2" t="n">
-        <v>97685</v>
+        <v>97691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867616</v>
       </c>
       <c r="B3" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136863103</v>
       </c>
       <c r="B2" t="n">
-        <v>97691</v>
+        <v>97703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136867616</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34987-2026 artfynd.xlsx
+++ b/artfynd/A 34987-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136867616</v>
       </c>
       <c r="B3" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
